--- a/results/Int Task Remove ACC -1.0/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_5_permute.xlsx
@@ -440,217 +440,217 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6220960189661532</v>
+        <v>0.6267763170861501</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6146169743692262</v>
+        <v>0.6269793951441467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6069644159376504</v>
+        <v>0.6332547535047683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6090261685611233</v>
+        <v>0.6320658493801368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6139686731858126</v>
+        <v>0.6267696299403929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6093179392891634</v>
+        <v>0.6267696299403929</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6038172339712635</v>
+        <v>0.6347463389636754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6038172339712635</v>
+        <v>0.6295240300823012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5995578740789337</v>
+        <v>0.6364019354711552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6016196267024065</v>
+        <v>0.6284495113456227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.60545664054691</v>
+        <v>0.6348607243516284</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6052454675229968</v>
+        <v>0.6404515301597313</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.604816434329413</v>
+        <v>0.6275375958373574</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6069091589963932</v>
+        <v>0.6288475724956991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6066307625598676</v>
+        <v>0.6311285931090019</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5641114261499779</v>
+        <v>0.6525249958469306</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5615748861777401</v>
+        <v>0.5867629005600308</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5416017896209866</v>
+        <v>0.5664895863542808</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5431968498616113</v>
+        <v>0.5662865082962842</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5558176056357856</v>
+        <v>0.5603177027753766</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5564659068191993</v>
+        <v>0.5512421901176656</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5564659068191993</v>
+        <v>0.5530660211341962</v>
       </c>
     </row>
     <row r="24">
@@ -660,667 +660,667 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5419449457848456</v>
+        <v>0.5566999569207032</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5422986605999003</v>
+        <v>0.5576857829873381</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5422986605999003</v>
+        <v>0.5327321706615911</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5422610014106357</v>
+        <v>0.529383318457367</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5414420020328923</v>
+        <v>0.5110563156220171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5366649162769351</v>
+        <v>0.5051346720764502</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5356643080986263</v>
+        <v>0.505497889677581</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5179303495054328</v>
+        <v>0.5111263546749484</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5209779281955407</v>
+        <v>0.4686767053629501</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4934205524849434</v>
+        <v>0.4651018980231389</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.495641036831391</v>
+        <v>0.4819658237578099</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5087270771682543</v>
+        <v>0.4825226166308612</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5029479754138287</v>
+        <v>0.4754740130476772</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5064245872975203</v>
+        <v>0.4737283160499945</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5041073153151124</v>
+        <v>0.4770690732883018</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4970682145180046</v>
+        <v>0.4507129201287311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4979639400944366</v>
+        <v>0.408029220715229</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4966849354796021</v>
+        <v>0.3979330384419373</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4934504686633311</v>
+        <v>0.3895959274578428</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4929619550680118</v>
+        <v>0.3812978834831723</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4837358056532426</v>
+        <v>0.3774098361578898</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4852569553354976</v>
+        <v>0.4025447053291624</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4856254522622262</v>
+        <v>0.4013100470493497</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4935645020962443</v>
+        <v>0.4065686072998291</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4930897147474793</v>
+        <v>0.4176266826970456</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4930897147474793</v>
+        <v>0.4092209404801793</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4926525865879789</v>
+        <v>0.4187860225983292</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4899886388913135</v>
+        <v>0.4186730450305356</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4923368829172287</v>
+        <v>0.4448398463786642</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5111333937757455</v>
+        <v>0.4541265320602885</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5161350268471304</v>
+        <v>0.4541265320602885</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5189203990325459</v>
+        <v>0.4092695102756794</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5409798850655622</v>
+        <v>0.4132839094602699</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5214745367567766</v>
+        <v>0.3968127655500776</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5214745367567766</v>
+        <v>0.3991515067899166</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5185561255662957</v>
+        <v>0.400971114345969</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5306549320163645</v>
+        <v>0.4186512238180646</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.568216981689891</v>
+        <v>0.4186512238180646</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5693601316593413</v>
+        <v>0.4114963298128445</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5664188433912698</v>
+        <v>0.4401257605748411</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5864151689806537</v>
+        <v>0.4434746127790652</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5752226467582126</v>
+        <v>0.455714553200116</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.577908415667349</v>
+        <v>0.4387686219411587</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5665828544398425</v>
+        <v>0.4617062357986141</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5715253590645317</v>
+        <v>0.4617062357986141</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5784799906520741</v>
+        <v>0.4611508507457223</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5931044264681453</v>
+        <v>0.492197156766406</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5744933959156322</v>
+        <v>0.5370408042595006</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5805403354553875</v>
+        <v>0.5329268017986311</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5641431021035649</v>
+        <v>0.54431958643875</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5608171269769315</v>
+        <v>0.5169666966063087</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5316527245543545</v>
+        <v>0.5240328979414853</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5214935423289287</v>
+        <v>0.5172560036490699</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5217518773281826</v>
+        <v>0.5172560036490699</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5093866409129432</v>
+        <v>0.5198287949904127</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5413269127348597</v>
+        <v>0.5198287949904127</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5283605371115472</v>
+        <v>0.5195127393646226</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5231396360503324</v>
+        <v>0.5075832232887242</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4989082354663685</v>
+        <v>0.5022922831745782</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4989082354663685</v>
+        <v>0.5204109286263335</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4903398900210891</v>
+        <v>0.5198460407873657</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4748922313667963</v>
+        <v>0.4826306668280967</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4789418260553724</v>
+        <v>0.4859323570569801</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4712906754439561</v>
+        <v>0.4893269634163854</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4716067310697463</v>
+        <v>0.4452973879304762</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4894680973873674</v>
+        <v>0.4938453622180489</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4888212040241131</v>
+        <v>0.4924210001717541</v>
       </c>
     </row>
   </sheetData>
